--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121701352</v>
+        <v>121701459</v>
       </c>
       <c r="B2" t="n">
-        <v>57363</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,51 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627008</v>
+        <v>627106</v>
       </c>
       <c r="R2" t="n">
-        <v>6894560</v>
+        <v>6894602</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121702597</v>
+        <v>121702107</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,41 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Rönningsån, Rönningsån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627376</v>
+        <v>627229</v>
       </c>
       <c r="R3" t="n">
-        <v>6894520</v>
+        <v>6894905</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121701029</v>
+        <v>121701352</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>57363</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,41 +916,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627013</v>
+        <v>627008</v>
       </c>
       <c r="R4" t="n">
-        <v>6894612</v>
+        <v>6894560</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ej möjligt att räkna antal pga snöläget.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121702107</v>
+        <v>121702191</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,43 +1038,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rönningsån, Rönningsån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627229</v>
+        <v>627214</v>
       </c>
       <c r="R5" t="n">
-        <v>6894905</v>
+        <v>6894907</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gick ej att räkna antal pga snöläget.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121701459</v>
+        <v>121702597</v>
       </c>
       <c r="B6" t="n">
-        <v>8425</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,25 +1155,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627106</v>
+        <v>627376</v>
       </c>
       <c r="R6" t="n">
-        <v>6894602</v>
+        <v>6894520</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121702191</v>
+        <v>121701029</v>
       </c>
       <c r="B8" t="n">
         <v>98113</v>
@@ -1408,14 +1408,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rönningsån, Rönningsån, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627214</v>
+        <v>627013</v>
       </c>
       <c r="R8" t="n">
-        <v>6894907</v>
+        <v>6894612</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gick ej att räkna antal pga snöläget.</t>
+          <t>Ej möjligt att räkna antal pga snöläget.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121701459</v>
+        <v>121701097</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627106</v>
+        <v>626983</v>
       </c>
       <c r="R2" t="n">
-        <v>6894602</v>
+        <v>6894591</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121702107</v>
+        <v>121702191</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rönningsån, Rönningsån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627229</v>
+        <v>627214</v>
       </c>
       <c r="R3" t="n">
-        <v>6894905</v>
+        <v>6894907</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gick ej att räkna antal pga snöläget.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121701352</v>
+        <v>121701459</v>
       </c>
       <c r="B4" t="n">
-        <v>57363</v>
+        <v>8425</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,51 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627008</v>
+        <v>627106</v>
       </c>
       <c r="R4" t="n">
-        <v>6894560</v>
+        <v>6894602</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121702191</v>
+        <v>121702107</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1033,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rönningsån, Rönningsån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627214</v>
+        <v>627229</v>
       </c>
       <c r="R5" t="n">
-        <v>6894907</v>
+        <v>6894905</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gick ej att räkna antal pga snöläget.</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1255,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121701097</v>
+        <v>121701029</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,46 +1262,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626983</v>
+        <v>627013</v>
       </c>
       <c r="R7" t="n">
-        <v>6894591</v>
+        <v>6894612</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ej möjligt att räkna antal pga snöläget.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121701029</v>
+        <v>121701352</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>57363</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,41 +1379,51 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627013</v>
+        <v>627008</v>
       </c>
       <c r="R8" t="n">
-        <v>6894612</v>
+        <v>6894560</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ej möjligt att räkna antal pga snöläget.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>121701352</v>
       </c>
       <c r="B8" t="n">
-        <v>57380</v>
+        <v>57385</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121701097</v>
+        <v>121701352</v>
       </c>
       <c r="B2" t="n">
-        <v>57385</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,9 +704,14 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626983</v>
+        <v>627008</v>
       </c>
       <c r="R2" t="n">
-        <v>6894591</v>
+        <v>6894560</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,53 +792,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121701029</v>
+        <v>121701097</v>
       </c>
       <c r="B3" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627013</v>
+        <v>626983</v>
       </c>
       <c r="R3" t="n">
-        <v>6894612</v>
+        <v>6894591</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ej möjligt att räkna antal pga snöläget.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,53 +904,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121702597</v>
+        <v>121702107</v>
       </c>
       <c r="B4" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Rönningsån, Rönningsån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627376</v>
+        <v>627229</v>
       </c>
       <c r="R4" t="n">
-        <v>6894520</v>
+        <v>6894905</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,55 +1016,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121702107</v>
+        <v>121701459</v>
       </c>
       <c r="B5" t="n">
-        <v>57385</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rönningsån, Rönningsån, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627229</v>
+        <v>627106</v>
       </c>
       <c r="R5" t="n">
-        <v>6894905</v>
+        <v>6894602</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,15 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121702191</v>
+        <v>121701029</v>
       </c>
       <c r="B6" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,14 +1154,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rönningsån, Rönningsån, Mpd</t>
+          <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627214</v>
+        <v>627013</v>
       </c>
       <c r="R6" t="n">
-        <v>6894907</v>
+        <v>6894612</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1213,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1203,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gick ej att räkna antal pga snöläget.</t>
+          <t>Ej möjligt att räkna antal pga snöläget.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,50 +1235,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121701459</v>
+        <v>121702191</v>
       </c>
       <c r="B7" t="n">
-        <v>8425</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Övertjärnen, Övertjärnen, Mpd</t>
+          <t>Rönningsån, Rönningsån, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627106</v>
+        <v>627214</v>
       </c>
       <c r="R7" t="n">
-        <v>6894602</v>
+        <v>6894907</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1330,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1315,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gick ej att räkna antal pga snöläget.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,63 +1347,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121701352</v>
+        <v>121702597</v>
       </c>
       <c r="B8" t="n">
-        <v>57385</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Övertjärnen, Övertjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627008</v>
+        <v>627376</v>
       </c>
       <c r="R8" t="n">
-        <v>6894560</v>
+        <v>6894520</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 60194-2024 artfynd.xlsx
+++ b/artfynd/A 60194-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121701352</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121701097</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121702107</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121701459</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121701029</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121702191</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,8 +1486,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121702597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>